--- a/Data/MST/OAD_2026_Schedule.xlsx
+++ b/Data/MST/OAD_2026_Schedule.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="91">
   <si>
     <t>start_date</t>
   </si>
@@ -36,6 +36,9 @@
     <t>event_type</t>
   </si>
   <si>
+    <t>defending_champ</t>
+  </si>
+  <si>
     <t>WM Phoenix Open</t>
   </si>
   <si>
@@ -54,24 +57,36 @@
     <t>SIGNATURE</t>
   </si>
   <si>
+    <t>Rory McIlroy</t>
+  </si>
+  <si>
     <t>The Genesis Invitational</t>
   </si>
   <si>
     <t>The Riviera Country Club</t>
   </si>
   <si>
+    <t>Ludvig Aberg</t>
+  </si>
+  <si>
     <t>Cognizant Classic</t>
   </si>
   <si>
     <t>Cognizant Classic in The Palm Beaches</t>
   </si>
   <si>
+    <t>Joe Highsmith</t>
+  </si>
+  <si>
     <t>Arnold Palmer Invitational presented by Mastercard</t>
   </si>
   <si>
     <t>Arnold Palmer's Bay Hill Club &amp; Lodge</t>
   </si>
   <si>
+    <t>Russel Henley</t>
+  </si>
+  <si>
     <t>THE PLAYERS Championship</t>
   </si>
   <si>
@@ -84,18 +99,27 @@
     <t>Innisbrook Resort (Copperhead Course)</t>
   </si>
   <si>
+    <t>Viktor Hovland</t>
+  </si>
+  <si>
     <t>Texas Children's Houston Open</t>
   </si>
   <si>
     <t>Memorial Park Golf Course</t>
   </si>
   <si>
+    <t>Min Woo Lee</t>
+  </si>
+  <si>
     <t>Valero Texas Open</t>
   </si>
   <si>
     <t>TPC San Antonio (Oaks Course)</t>
   </si>
   <si>
+    <t>Brian Harman</t>
+  </si>
+  <si>
     <t>Masters Tournament</t>
   </si>
   <si>
@@ -111,6 +135,9 @@
     <t>Harbour Town Golf Links</t>
   </si>
   <si>
+    <t>Justin Thomas</t>
+  </si>
+  <si>
     <t>Cadillac Championship</t>
   </si>
   <si>
@@ -123,18 +150,27 @@
     <t>Quail Hollow Club</t>
   </si>
   <si>
+    <t>Sepp Straka</t>
+  </si>
+  <si>
     <t>PGA Championship</t>
   </si>
   <si>
     <t>Aronimink GC</t>
   </si>
   <si>
+    <t>Scottie Scheffler</t>
+  </si>
+  <si>
     <t>THE CJ CUP Byron Nelson</t>
   </si>
   <si>
     <t>TPC Craig Ranch</t>
   </si>
   <si>
+    <t>Ben Griffin</t>
+  </si>
+  <si>
     <t>Charles Schwab Challenge</t>
   </si>
   <si>
@@ -147,30 +183,45 @@
     <t>Muirfield Village Golf Club</t>
   </si>
   <si>
+    <t>Ryan Fox</t>
+  </si>
+  <si>
     <t>RBC Canadian Open</t>
   </si>
   <si>
     <t>TPC Toronto at Osprey Valley (North Course)</t>
   </si>
   <si>
+    <t>J.J. Spaun</t>
+  </si>
+  <si>
     <t>U.S. Open</t>
   </si>
   <si>
     <t>Shinnecock Hills GC</t>
   </si>
   <si>
+    <t>Keegan Bradley</t>
+  </si>
+  <si>
     <t>Travelers Championship</t>
   </si>
   <si>
     <t>TPC River Highlands</t>
   </si>
   <si>
+    <t>Brian Campbell</t>
+  </si>
+  <si>
     <t>John Deere Classic</t>
   </si>
   <si>
     <t>TPC Deere Run</t>
   </si>
   <si>
+    <t>Chris Gotterup</t>
+  </si>
+  <si>
     <t>Genesis Scottish Open</t>
   </si>
   <si>
@@ -183,24 +234,36 @@
     <t>Royal Birkdale GC</t>
   </si>
   <si>
+    <t>Kurt Kitayama</t>
+  </si>
+  <si>
     <t>3M Open</t>
   </si>
   <si>
     <t>TPC Twin Cities</t>
   </si>
   <si>
+    <t>Aldrich Potgieter</t>
+  </si>
+  <si>
     <t>Rocket Classic</t>
   </si>
   <si>
     <t>Detroit Golf Club</t>
   </si>
   <si>
+    <t>Cameron Young</t>
+  </si>
+  <si>
     <t>Wyndham Championship</t>
   </si>
   <si>
     <t>Sedgefield Country Club</t>
   </si>
   <si>
+    <t>Justin Rose</t>
+  </si>
+  <si>
     <t>FedEx St. Jude Championship</t>
   </si>
   <si>
@@ -214,6 +277,9 @@
   </si>
   <si>
     <t>Bellerive CC</t>
+  </si>
+  <si>
+    <t>Tommy Fleetwood</t>
   </si>
   <si>
     <t>Tour Championship</t>
@@ -272,7 +338,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -313,6 +379,9 @@
       <alignment horizontal="left"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="3" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="166" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
@@ -547,7 +616,7 @@
     <col customWidth="1" min="4" max="4" width="9.38"/>
     <col customWidth="1" min="5" max="5" width="13.0"/>
     <col customWidth="1" min="6" max="6" width="31.25"/>
-    <col customWidth="1" min="7" max="7" width="25.25"/>
+    <col customWidth="1" min="7" max="10" width="25.25"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -572,6 +641,11 @@
       <c r="G1" s="7" t="s">
         <v>6</v>
       </c>
+      <c r="H1" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="7"/>
+      <c r="J1" s="7"/>
     </row>
     <row r="2">
       <c r="A2" s="8">
@@ -581,7 +655,7 @@
         <v>3.0</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D2" s="10">
         <v>9600000.0</v>
@@ -590,10 +664,10 @@
         <v>1728000.0</v>
       </c>
       <c r="F2" s="12" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G2" s="13" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3">
@@ -604,7 +678,7 @@
         <v>5.0</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D3" s="10">
         <v>2.0E7</v>
@@ -613,11 +687,16 @@
         <v>3600000.0</v>
       </c>
       <c r="F3" s="12" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G3" s="13" t="s">
-        <v>12</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="H3" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="I3" s="14"/>
+      <c r="J3" s="13"/>
     </row>
     <row r="4">
       <c r="A4" s="8">
@@ -627,20 +706,25 @@
         <v>7.0</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D4" s="10">
         <v>2.0E7</v>
       </c>
-      <c r="E4" s="14">
+      <c r="E4" s="15">
         <v>4000000.0</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G4" s="13" t="s">
-        <v>12</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="H4" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="I4" s="13"/>
+      <c r="J4" s="13"/>
     </row>
     <row r="5">
       <c r="A5" s="8">
@@ -650,7 +734,7 @@
         <v>10.0</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D5" s="10">
         <v>9600000.0</v>
@@ -659,11 +743,16 @@
         <v>1728000.0</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G5" s="13" t="s">
-        <v>9</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="H5" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="I5" s="13"/>
+      <c r="J5" s="13"/>
     </row>
     <row r="6">
       <c r="A6" s="8">
@@ -673,20 +762,25 @@
         <v>9.0</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D6" s="10">
         <v>2.0E7</v>
       </c>
-      <c r="E6" s="14">
+      <c r="E6" s="15">
         <v>4000000.0</v>
       </c>
       <c r="F6" s="12" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="G6" s="13" t="s">
-        <v>12</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="H6" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="I6" s="13"/>
+      <c r="J6" s="13"/>
     </row>
     <row r="7">
       <c r="A7" s="8">
@@ -696,20 +790,25 @@
         <v>11.0</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D7" s="10">
         <v>2.777777777E7</v>
       </c>
-      <c r="E7" s="14">
+      <c r="E7" s="15">
         <v>5000000.0</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G7" s="13" t="s">
-        <v>12</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="H7" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="I7" s="13"/>
+      <c r="J7" s="13"/>
     </row>
     <row r="8">
       <c r="A8" s="8">
@@ -719,7 +818,7 @@
         <v>475.0</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="D8" s="10">
         <v>9100000.0</v>
@@ -728,11 +827,16 @@
         <v>1638000.0</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="G8" s="13" t="s">
-        <v>9</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="H8" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="I8" s="13"/>
+      <c r="J8" s="13"/>
     </row>
     <row r="9">
       <c r="A9" s="8">
@@ -742,7 +846,7 @@
         <v>20.0</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D9" s="10">
         <v>9900000.0</v>
@@ -751,11 +855,16 @@
         <v>1782000.0</v>
       </c>
       <c r="F9" s="12" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="G9" s="13" t="s">
-        <v>9</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="H9" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="I9" s="13"/>
+      <c r="J9" s="13"/>
     </row>
     <row r="10">
       <c r="A10" s="8">
@@ -765,7 +874,7 @@
         <v>41.0</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="D10" s="10">
         <v>9800000.0</v>
@@ -774,11 +883,16 @@
         <v>1764000.0</v>
       </c>
       <c r="F10" s="12" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="G10" s="13" t="s">
-        <v>9</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="H10" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="I10" s="13"/>
+      <c r="J10" s="13"/>
     </row>
     <row r="11">
       <c r="A11" s="8">
@@ -788,20 +902,25 @@
         <v>14.0</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="D11" s="10">
         <v>2.777777777E7</v>
       </c>
-      <c r="E11" s="14">
+      <c r="E11" s="15">
         <v>5000000.0</v>
       </c>
       <c r="F11" s="12" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="G11" s="13" t="s">
-        <v>29</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="H11" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="I11" s="13"/>
+      <c r="J11" s="13"/>
     </row>
     <row r="12">
       <c r="A12" s="8">
@@ -811,7 +930,7 @@
         <v>12.0</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="D12" s="10">
         <v>2.0E7</v>
@@ -820,11 +939,16 @@
         <v>3600000.0</v>
       </c>
       <c r="F12" s="12" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="G12" s="13" t="s">
-        <v>12</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="H12" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="I12" s="13"/>
+      <c r="J12" s="13"/>
     </row>
     <row r="13">
       <c r="A13" s="8">
@@ -832,7 +956,7 @@
       </c>
       <c r="B13" s="9"/>
       <c r="C13" s="9" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="D13" s="10">
         <v>2.0E7</v>
@@ -840,12 +964,15 @@
       <c r="E13" s="11">
         <v>3600000.0</v>
       </c>
-      <c r="F13" s="15" t="s">
-        <v>33</v>
+      <c r="F13" s="16" t="s">
+        <v>42</v>
       </c>
       <c r="G13" s="13" t="s">
-        <v>12</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="H13" s="13"/>
+      <c r="I13" s="13"/>
+      <c r="J13" s="13"/>
     </row>
     <row r="14">
       <c r="A14" s="8">
@@ -855,7 +982,7 @@
         <v>480.0</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="D14" s="10">
         <v>2.0E7</v>
@@ -864,11 +991,16 @@
         <v>3600000.0</v>
       </c>
       <c r="F14" s="12" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="G14" s="13" t="s">
-        <v>12</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="H14" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="I14" s="13"/>
+      <c r="J14" s="13"/>
     </row>
     <row r="15">
       <c r="A15" s="8">
@@ -878,20 +1010,25 @@
         <v>33.0</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="D15" s="10">
         <v>2.777777777E7</v>
       </c>
-      <c r="E15" s="14">
+      <c r="E15" s="15">
         <v>5000000.0</v>
       </c>
-      <c r="F15" s="15" t="s">
+      <c r="F15" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="G15" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="G15" s="13" t="s">
-        <v>29</v>
-      </c>
+      <c r="H15" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="I15" s="13"/>
+      <c r="J15" s="13"/>
     </row>
     <row r="16">
       <c r="A16" s="8">
@@ -901,7 +1038,7 @@
         <v>19.0</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="D16" s="10">
         <v>1.03E7</v>
@@ -910,11 +1047,16 @@
         <v>1854000.0</v>
       </c>
       <c r="F16" s="12" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="G16" s="13" t="s">
-        <v>9</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="H16" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="I16" s="13"/>
+      <c r="J16" s="13"/>
     </row>
     <row r="17">
       <c r="A17" s="8">
@@ -924,7 +1066,7 @@
         <v>21.0</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="D17" s="10">
         <v>9900000.0</v>
@@ -933,11 +1075,16 @@
         <v>1782000.0</v>
       </c>
       <c r="F17" s="12" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="G17" s="13" t="s">
-        <v>9</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="H17" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="I17" s="13"/>
+      <c r="J17" s="13"/>
     </row>
     <row r="18">
       <c r="A18" s="8">
@@ -947,20 +1094,25 @@
         <v>23.0</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="D18" s="10">
         <v>2.0E7</v>
       </c>
-      <c r="E18" s="14">
+      <c r="E18" s="15">
         <v>4000000.0</v>
       </c>
       <c r="F18" s="12" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="G18" s="13" t="s">
-        <v>12</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="H18" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="I18" s="13"/>
+      <c r="J18" s="13"/>
     </row>
     <row r="19">
       <c r="A19" s="8">
@@ -970,7 +1122,7 @@
         <v>32.0</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="D19" s="10">
         <v>9800000.0</v>
@@ -978,12 +1130,17 @@
       <c r="E19" s="11">
         <v>1764000.0</v>
       </c>
-      <c r="F19" s="15" t="s">
-        <v>45</v>
+      <c r="F19" s="16" t="s">
+        <v>58</v>
       </c>
       <c r="G19" s="13" t="s">
-        <v>9</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="H19" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="I19" s="13"/>
+      <c r="J19" s="13"/>
     </row>
     <row r="20">
       <c r="A20" s="8">
@@ -993,20 +1150,25 @@
         <v>26.0</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="D20" s="10">
         <v>2.777777777E7</v>
       </c>
-      <c r="E20" s="14">
+      <c r="E20" s="15">
         <v>5000000.0</v>
       </c>
-      <c r="F20" s="15" t="s">
-        <v>47</v>
+      <c r="F20" s="16" t="s">
+        <v>61</v>
       </c>
       <c r="G20" s="13" t="s">
-        <v>29</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="H20" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="I20" s="13"/>
+      <c r="J20" s="13"/>
     </row>
     <row r="21">
       <c r="A21" s="8">
@@ -1016,7 +1178,7 @@
         <v>34.0</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="D21" s="10">
         <v>2.0E7</v>
@@ -1025,11 +1187,16 @@
         <v>3600000.0</v>
       </c>
       <c r="F21" s="12" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="G21" s="13" t="s">
-        <v>12</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="H21" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="I21" s="13"/>
+      <c r="J21" s="13"/>
     </row>
     <row r="22">
       <c r="A22" s="8">
@@ -1039,7 +1206,7 @@
         <v>30.0</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="D22" s="10">
         <v>8800000.0</v>
@@ -1048,11 +1215,16 @@
         <v>1584000.0</v>
       </c>
       <c r="F22" s="12" t="s">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="G22" s="13" t="s">
-        <v>9</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="H22" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="I22" s="13"/>
+      <c r="J22" s="13"/>
     </row>
     <row r="23">
       <c r="A23" s="8">
@@ -1062,7 +1234,7 @@
         <v>541.0</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="D23" s="10">
         <v>9000000.0</v>
@@ -1071,11 +1243,16 @@
         <v>1620000.0</v>
       </c>
       <c r="F23" s="12" t="s">
-        <v>53</v>
+        <v>70</v>
       </c>
       <c r="G23" s="13" t="s">
-        <v>9</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="H23" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="I23" s="13"/>
+      <c r="J23" s="13"/>
     </row>
     <row r="24">
       <c r="A24" s="8">
@@ -1085,20 +1262,25 @@
         <v>100.0</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>54</v>
+        <v>71</v>
       </c>
       <c r="D24" s="10">
         <v>2.777777777E7</v>
       </c>
-      <c r="E24" s="14">
+      <c r="E24" s="15">
         <v>5000000.0</v>
       </c>
-      <c r="F24" s="15" t="s">
-        <v>55</v>
+      <c r="F24" s="16" t="s">
+        <v>72</v>
       </c>
       <c r="G24" s="13" t="s">
-        <v>29</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="H24" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="I24" s="13"/>
+      <c r="J24" s="13"/>
     </row>
     <row r="25">
       <c r="A25" s="8">
@@ -1108,7 +1290,7 @@
         <v>525.0</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="D25" s="10">
         <v>8800000.0</v>
@@ -1117,11 +1299,16 @@
         <v>1584000.0</v>
       </c>
       <c r="F25" s="12" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="G25" s="13" t="s">
-        <v>9</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="H25" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="I25" s="13"/>
+      <c r="J25" s="13"/>
     </row>
     <row r="26">
       <c r="A26" s="8">
@@ -1131,7 +1318,7 @@
         <v>524.0</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>58</v>
+        <v>77</v>
       </c>
       <c r="D26" s="10">
         <v>1.0E7</v>
@@ -1140,11 +1327,16 @@
         <v>1800000.0</v>
       </c>
       <c r="F26" s="12" t="s">
-        <v>59</v>
+        <v>78</v>
       </c>
       <c r="G26" s="13" t="s">
-        <v>9</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="H26" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="I26" s="13"/>
+      <c r="J26" s="13"/>
     </row>
     <row r="27">
       <c r="A27" s="8">
@@ -1154,7 +1346,7 @@
         <v>13.0</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="D27" s="10">
         <v>8500000.0</v>
@@ -1163,11 +1355,16 @@
         <v>1530000.0</v>
       </c>
       <c r="F27" s="12" t="s">
-        <v>61</v>
+        <v>81</v>
       </c>
       <c r="G27" s="13" t="s">
-        <v>9</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="H27" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="I27" s="13"/>
+      <c r="J27" s="13"/>
     </row>
     <row r="28">
       <c r="A28" s="8">
@@ -1177,7 +1374,7 @@
         <v>27.0</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>62</v>
+        <v>83</v>
       </c>
       <c r="D28" s="10">
         <v>2.0E7</v>
@@ -1186,11 +1383,16 @@
         <v>3600000.0</v>
       </c>
       <c r="F28" s="12" t="s">
-        <v>63</v>
+        <v>84</v>
       </c>
       <c r="G28" s="13" t="s">
-        <v>64</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="H28" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="I28" s="13"/>
+      <c r="J28" s="13"/>
     </row>
     <row r="29">
       <c r="A29" s="8">
@@ -1200,7 +1402,7 @@
         <v>28.0</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>65</v>
+        <v>86</v>
       </c>
       <c r="D29" s="10">
         <v>2.0E7</v>
@@ -1208,33 +1410,41 @@
       <c r="E29" s="11">
         <v>3600000.0</v>
       </c>
-      <c r="F29" s="15" t="s">
-        <v>66</v>
+      <c r="F29" s="16" t="s">
+        <v>87</v>
       </c>
       <c r="G29" s="13" t="s">
-        <v>64</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="H29" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="I29" s="13"/>
+      <c r="J29" s="13"/>
     </row>
     <row r="30">
-      <c r="A30" s="16">
+      <c r="A30" s="17">
         <v>46261.0</v>
       </c>
       <c r="B30" s="9"/>
-      <c r="C30" s="15" t="s">
-        <v>67</v>
+      <c r="C30" s="16" t="s">
+        <v>89</v>
       </c>
       <c r="D30" s="10">
         <v>2.777777777E7</v>
       </c>
-      <c r="E30" s="14">
+      <c r="E30" s="15">
         <v>5000000.0</v>
       </c>
-      <c r="F30" s="15" t="s">
-        <v>68</v>
+      <c r="F30" s="16" t="s">
+        <v>90</v>
       </c>
       <c r="G30" s="13" t="s">
-        <v>64</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="H30" s="13"/>
+      <c r="I30" s="13"/>
+      <c r="J30" s="13"/>
     </row>
   </sheetData>
   <autoFilter ref="$A$1:$G$30">

--- a/Data/MST/OAD_2026_Schedule.xlsx
+++ b/Data/MST/OAD_2026_Schedule.xlsx
@@ -6,14 +6,14 @@
     <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">Sheet1!$A$1:$G$30</definedName>
+    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">Sheet1!$A$1:$H$30</definedName>
   </definedNames>
   <calcPr/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="120">
   <si>
     <t>start_date</t>
   </si>
@@ -33,16 +33,22 @@
     <t>course_name</t>
   </si>
   <si>
+    <t>course_num</t>
+  </si>
+  <si>
     <t>event_type</t>
   </si>
   <si>
     <t>defending_champ</t>
   </si>
   <si>
+    <t>image</t>
+  </si>
+  <si>
     <t>WM Phoenix Open</t>
   </si>
   <si>
-    <t>TPC Scottsdale (Stadium Course)</t>
+    <t>TPC Scottsdale</t>
   </si>
   <si>
     <t>REGULAR</t>
@@ -51,7 +57,7 @@
     <t>AT&amp;T Pebble Beach Pro-Am</t>
   </si>
   <si>
-    <t>Pebble Beach Golf Links</t>
+    <t>Pebble Beach</t>
   </si>
   <si>
     <t>SIGNATURE</t>
@@ -60,90 +66,123 @@
     <t>Rory McIlroy</t>
   </si>
   <si>
+    <t>https://res.cloudinary.com/pgatour-prod/d_tournaments:logos:R000.png/tournaments/logos/R005.png</t>
+  </si>
+  <si>
     <t>The Genesis Invitational</t>
   </si>
   <si>
-    <t>The Riviera Country Club</t>
+    <t>Riviera Country Club</t>
   </si>
   <si>
     <t>Ludvig Aberg</t>
   </si>
   <si>
+    <t>https://res.cloudinary.com/pgatour-prod/image/upload/dpr_2.0,q_auto/c_scale,w_200/v1/tournaments/logos/r007?_a=DAJHqpB3ZAAB</t>
+  </si>
+  <si>
     <t>Cognizant Classic</t>
   </si>
   <si>
-    <t>Cognizant Classic in The Palm Beaches</t>
+    <t>PGA National</t>
   </si>
   <si>
     <t>Joe Highsmith</t>
   </si>
   <si>
+    <t>https://res.cloudinary.com/pgatour-prod/image/upload/dpr_2.0,q_auto/c_scale,w_200/v1/tournaments/logos/r010?_a=DAJHqpB3ZAAB</t>
+  </si>
+  <si>
     <t>Arnold Palmer Invitational presented by Mastercard</t>
   </si>
   <si>
-    <t>Arnold Palmer's Bay Hill Club &amp; Lodge</t>
+    <t>Bay Hill</t>
   </si>
   <si>
     <t>Russel Henley</t>
   </si>
   <si>
+    <t>https://res.cloudinary.com/pgatour-prod/image/upload/dpr_2.0,q_auto/c_scale,w_200/v1/tournaments/logos/r009?_a=DAJHqpB3ZAAB</t>
+  </si>
+  <si>
     <t>THE PLAYERS Championship</t>
   </si>
   <si>
-    <t>TPC Sawgrass (THE PLAYERS Stadium Course)</t>
+    <t>TPC Sawgrass</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/pgatour-prod/image/upload/dpr_2.0,q_auto/c_scale,w_200/v1/tournaments/logos/r011?_a=DAJHqpB3ZAAB</t>
   </si>
   <si>
     <t>Valspar Championship</t>
   </si>
   <si>
-    <t>Innisbrook Resort (Copperhead Course)</t>
+    <t>Innisbrook Resort</t>
   </si>
   <si>
     <t>Viktor Hovland</t>
   </si>
   <si>
+    <t>https://res.cloudinary.com/pgatour-prod/image/upload/dpr_2.0,q_auto/c_scale,w_200/v1/tournaments/logos/r475?_a=DAJHqpB3ZAAB</t>
+  </si>
+  <si>
     <t>Texas Children's Houston Open</t>
   </si>
   <si>
-    <t>Memorial Park Golf Course</t>
+    <t>Memorial Park</t>
   </si>
   <si>
     <t>Min Woo Lee</t>
   </si>
   <si>
+    <t>https://res.cloudinary.com/pgatour-prod/image/upload/dpr_2.0,q_auto/c_scale,w_200/v1/tournaments/logos/r020?_a=DAJHqpB3ZAAB</t>
+  </si>
+  <si>
     <t>Valero Texas Open</t>
   </si>
   <si>
-    <t>TPC San Antonio (Oaks Course)</t>
+    <t>TPC San Antonio</t>
   </si>
   <si>
     <t>Brian Harman</t>
   </si>
   <si>
+    <t>https://res.cloudinary.com/pgatour-prod/image/upload/dpr_2.0,q_auto/c_scale,w_200/v1/tournaments/logos/r041?_a=DAJHqpB3ZAAB</t>
+  </si>
+  <si>
     <t>Masters Tournament</t>
   </si>
   <si>
-    <t>Augusta National Golf Club</t>
+    <t>Augusta National</t>
   </si>
   <si>
     <t>MAJOR</t>
   </si>
   <si>
+    <t>https://res.cloudinary.com/pgatour-prod/image/upload/dpr_2.0,q_auto/c_scale,w_200/v1/tournaments/logos/r014?_a=DAJHqpB3ZAAB</t>
+  </si>
+  <si>
     <t>RBC Heritage</t>
   </si>
   <si>
-    <t>Harbour Town Golf Links</t>
+    <t>Harbour Town</t>
   </si>
   <si>
     <t>Justin Thomas</t>
   </si>
   <si>
+    <t>https://res.cloudinary.com/pgatour-prod/image/upload/dpr_2.0,q_auto/c_scale,w_200/v1/tournaments/logos/r012?_a=DAJHqpB3ZAAB</t>
+  </si>
+  <si>
     <t>Cadillac Championship</t>
   </si>
   <si>
     <t>Trump National Doral</t>
   </si>
   <si>
+    <t>https://res.cloudinary.com/pgatour-prod/image/upload/dpr_2.0,q_auto/c_scale,w_200/v1/tournaments/logos/r556?_a=DAJHqpB3ZAAB</t>
+  </si>
+  <si>
     <t>Truist Championship</t>
   </si>
   <si>
@@ -153,6 +192,9 @@
     <t>Sepp Straka</t>
   </si>
   <si>
+    <t>https://res.cloudinary.com/pgatour-prod/image/upload/dpr_2.0,q_auto/c_scale,w_200/v1/tournaments/logos/r480?_a=DAJHqpB3ZAAB</t>
+  </si>
+  <si>
     <t>PGA Championship</t>
   </si>
   <si>
@@ -162,115 +204,154 @@
     <t>Scottie Scheffler</t>
   </si>
   <si>
+    <t>https://res.cloudinary.com/pgatour-prod/image/upload/dpr_2.0,q_auto/c_scale,w_200/v1/tournaments/logos/r033?_a=DAJHqpB3ZAAB</t>
+  </si>
+  <si>
     <t>THE CJ CUP Byron Nelson</t>
   </si>
   <si>
     <t>TPC Craig Ranch</t>
   </si>
   <si>
+    <t>https://res.cloudinary.com/pgatour-prod/image/upload/dpr_2.0,q_auto/c_scale,w_200/v1/tournaments/logos/r019?_a=DAJHqpB3ZAAB</t>
+  </si>
+  <si>
+    <t>Charles Schwab Challenge</t>
+  </si>
+  <si>
+    <t>Colonial Country Club</t>
+  </si>
+  <si>
     <t>Ben Griffin</t>
   </si>
   <si>
-    <t>Charles Schwab Challenge</t>
-  </si>
-  <si>
-    <t>Colonial Country Club</t>
+    <t>https://res.cloudinary.com/pgatour-prod/image/upload/dpr_2.0,q_auto/c_scale,w_200/v1/tournaments/logos/r023?_a=DAJHqpB3ZAAB</t>
   </si>
   <si>
     <t>the Memorial Tournament presented by Workday</t>
   </si>
   <si>
-    <t>Muirfield Village Golf Club</t>
+    <t>Muirfield Village</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/pgatour-prod/image/upload/dpr_2.0,q_auto/c_scale,w_200/v1/tournaments/logos/r032?_a=DAJHqpB3ZAAB</t>
+  </si>
+  <si>
+    <t>RBC Canadian Open</t>
+  </si>
+  <si>
+    <t>TPC Toronto</t>
   </si>
   <si>
     <t>Ryan Fox</t>
   </si>
   <si>
-    <t>RBC Canadian Open</t>
-  </si>
-  <si>
-    <t>TPC Toronto at Osprey Valley (North Course)</t>
+    <t>U.S. Open</t>
+  </si>
+  <si>
+    <t>Shinnecock Hills GC</t>
   </si>
   <si>
     <t>J.J. Spaun</t>
   </si>
   <si>
-    <t>U.S. Open</t>
-  </si>
-  <si>
-    <t>Shinnecock Hills GC</t>
+    <t>https://res.cloudinary.com/pgatour-prod/image/upload/dpr_2.0,q_auto/c_scale,w_200/v1/tournaments/logos/r026?_a=DAJHqpB3ZAAB</t>
+  </si>
+  <si>
+    <t>Travelers Championship</t>
+  </si>
+  <si>
+    <t>TPC River Highlands</t>
   </si>
   <si>
     <t>Keegan Bradley</t>
   </si>
   <si>
-    <t>Travelers Championship</t>
-  </si>
-  <si>
-    <t>TPC River Highlands</t>
+    <t>https://res.cloudinary.com/pgatour-prod/image/upload/dpr_2.0,q_auto/c_scale,w_200/v1/tournaments/logos/r034?_a=DAJHqpB3ZAAB</t>
+  </si>
+  <si>
+    <t>John Deere Classic</t>
+  </si>
+  <si>
+    <t>TPC Deere Run</t>
   </si>
   <si>
     <t>Brian Campbell</t>
   </si>
   <si>
-    <t>John Deere Classic</t>
-  </si>
-  <si>
-    <t>TPC Deere Run</t>
+    <t>https://res.cloudinary.com/pgatour-prod/image/upload/dpr_2.0,q_auto/c_scale,w_200/v1/tournaments/logos/r030?_a=DAJHqpB3ZAAB</t>
+  </si>
+  <si>
+    <t>Genesis Scottish Open</t>
+  </si>
+  <si>
+    <t>The Renaissance Club</t>
   </si>
   <si>
     <t>Chris Gotterup</t>
   </si>
   <si>
-    <t>Genesis Scottish Open</t>
-  </si>
-  <si>
-    <t>The Renaissance Club</t>
+    <t>https://res.cloudinary.com/pgatour-prod/image/upload/dpr_2.0,q_auto/c_scale,w_200/v1/tournaments/logos/r541?_a=DAJHqpB3ZAAB</t>
   </si>
   <si>
     <t>The Open Championship</t>
   </si>
   <si>
-    <t>Royal Birkdale GC</t>
+    <t>Royal Birkdale</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/pgatour-prod/image/upload/dpr_2.0,q_auto/c_scale,w_200/v1/tournaments/logos/r100?_a=DAJHqpB3ZAAB</t>
+  </si>
+  <si>
+    <t>3M Open</t>
+  </si>
+  <si>
+    <t>TPC Twin Cities</t>
   </si>
   <si>
     <t>Kurt Kitayama</t>
   </si>
   <si>
-    <t>3M Open</t>
-  </si>
-  <si>
-    <t>TPC Twin Cities</t>
+    <t>https://res.cloudinary.com/pgatour-prod/image/upload/dpr_2.0,q_auto/c_scale,w_200/v1/tournaments/logos/r525?_a=DAJHqpB3ZAAB</t>
+  </si>
+  <si>
+    <t>Rocket Classic</t>
+  </si>
+  <si>
+    <t>Detroit Golf Club</t>
   </si>
   <si>
     <t>Aldrich Potgieter</t>
   </si>
   <si>
-    <t>Rocket Classic</t>
-  </si>
-  <si>
-    <t>Detroit Golf Club</t>
+    <t>https://res.cloudinary.com/pgatour-prod/image/upload/dpr_2.0,q_auto/c_scale,w_200/v1/tournaments/logos/r524?_a=DAJHqpB3ZAAB</t>
+  </si>
+  <si>
+    <t>Wyndham Championship</t>
+  </si>
+  <si>
+    <t>Sedgefield Country Club</t>
   </si>
   <si>
     <t>Cameron Young</t>
   </si>
   <si>
-    <t>Wyndham Championship</t>
-  </si>
-  <si>
-    <t>Sedgefield Country Club</t>
+    <t>https://res.cloudinary.com/pgatour-prod/image/upload/dpr_2.0,q_auto/c_scale,w_200/v1/tournaments/logos/r013?_a=DAJHqpB3ZAAB</t>
+  </si>
+  <si>
+    <t>FedEx St. Jude Championship</t>
+  </si>
+  <si>
+    <t>TPC Southwind</t>
+  </si>
+  <si>
+    <t>PLAYOFFS</t>
   </si>
   <si>
     <t>Justin Rose</t>
   </si>
   <si>
-    <t>FedEx St. Jude Championship</t>
-  </si>
-  <si>
-    <t>TPC Southwind</t>
-  </si>
-  <si>
-    <t>PLAYOFFS</t>
+    <t>https://res.cloudinary.com/pgatour-prod/image/upload/dpr_2.0,q_auto/c_scale,w_200/v1/tournaments/logos/r027?_a=DAJHqpB3ZAAB</t>
   </si>
   <si>
     <t>BMW Championship</t>
@@ -279,13 +360,19 @@
     <t>Bellerive CC</t>
   </si>
   <si>
+    <t>https://res.cloudinary.com/pgatour-prod/image/upload/dpr_2.0,q_auto/c_scale,w_200/v1/tournaments/logos/r028?_a=DAJHqpB3ZAAB</t>
+  </si>
+  <si>
+    <t>Tour Championship</t>
+  </si>
+  <si>
+    <t>East Lake</t>
+  </si>
+  <si>
     <t>Tommy Fleetwood</t>
   </si>
   <si>
-    <t>Tour Championship</t>
-  </si>
-  <si>
-    <t>East Lake Golf Club</t>
+    <t>https://res.cloudinary.com/pgatour-prod/image/upload/dpr_2.0,q_auto/c_scale,w_200/v1/tournaments/logos/r060?_a=DAJHqpB3ZAAB</t>
   </si>
 </sst>
 </file>
@@ -297,7 +384,7 @@
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0"/>
     <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="7">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -323,6 +410,16 @@
       <color theme="1"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <u/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <u/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -338,7 +435,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="21">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -376,19 +473,28 @@
       <alignment horizontal="left"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left"/>
+      <alignment horizontal="left" readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="3" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="3" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="166" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" readingOrder="0"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0"/>
+      <alignment horizontal="left"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="3" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" readingOrder="0"/>
@@ -616,7 +722,7 @@
     <col customWidth="1" min="4" max="4" width="9.38"/>
     <col customWidth="1" min="5" max="5" width="13.0"/>
     <col customWidth="1" min="6" max="6" width="31.25"/>
-    <col customWidth="1" min="7" max="10" width="25.25"/>
+    <col customWidth="1" min="7" max="11" width="25.25"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -638,14 +744,19 @@
       <c r="F1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
       <c r="H1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="7"/>
-      <c r="J1" s="7"/>
+      <c r="I1" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="7"/>
     </row>
     <row r="2">
       <c r="A2" s="8">
@@ -655,7 +766,7 @@
         <v>3.0</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D2" s="10">
         <v>9600000.0</v>
@@ -664,10 +775,13 @@
         <v>1728000.0</v>
       </c>
       <c r="F2" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="G2" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="G2" s="13">
+        <v>510.0</v>
+      </c>
+      <c r="H2" s="14" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="3">
@@ -678,7 +792,7 @@
         <v>5.0</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D3" s="10">
         <v>2.0E7</v>
@@ -687,16 +801,21 @@
         <v>3600000.0</v>
       </c>
       <c r="F3" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="G3" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="H3" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="I3" s="14"/>
-      <c r="J3" s="13"/>
+      <c r="G3" s="13">
+        <v>5.0</v>
+      </c>
+      <c r="H3" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="I3" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="J3" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="K3" s="14"/>
     </row>
     <row r="4">
       <c r="A4" s="8">
@@ -706,25 +825,30 @@
         <v>7.0</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D4" s="10">
         <v>2.0E7</v>
       </c>
-      <c r="E4" s="15">
+      <c r="E4" s="16">
         <v>4000000.0</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="G4" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="H4" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="I4" s="13"/>
-      <c r="J4" s="13"/>
+        <v>19</v>
+      </c>
+      <c r="G4" s="13">
+        <v>500.0</v>
+      </c>
+      <c r="H4" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="I4" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="J4" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="K4" s="14"/>
     </row>
     <row r="5">
       <c r="A5" s="8">
@@ -734,7 +858,7 @@
         <v>10.0</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D5" s="10">
         <v>9600000.0</v>
@@ -743,16 +867,21 @@
         <v>1728000.0</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="G5" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="H5" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="I5" s="13"/>
-      <c r="J5" s="13"/>
+        <v>23</v>
+      </c>
+      <c r="G5" s="13">
+        <v>734.0</v>
+      </c>
+      <c r="H5" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="I5" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="J5" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="K5" s="14"/>
     </row>
     <row r="6">
       <c r="A6" s="8">
@@ -762,25 +891,30 @@
         <v>9.0</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="D6" s="10">
         <v>2.0E7</v>
       </c>
-      <c r="E6" s="15">
+      <c r="E6" s="16">
         <v>4000000.0</v>
       </c>
       <c r="F6" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="G6" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="H6" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="I6" s="13"/>
-      <c r="J6" s="13"/>
+        <v>27</v>
+      </c>
+      <c r="G6" s="13">
+        <v>9.0</v>
+      </c>
+      <c r="H6" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="I6" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="J6" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="K6" s="14"/>
     </row>
     <row r="7">
       <c r="A7" s="8">
@@ -790,25 +924,30 @@
         <v>11.0</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="D7" s="10">
         <v>2.777777777E7</v>
       </c>
-      <c r="E7" s="15">
+      <c r="E7" s="16">
         <v>5000000.0</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="G7" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="H7" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="I7" s="13"/>
-      <c r="J7" s="13"/>
+        <v>31</v>
+      </c>
+      <c r="G7" s="13">
+        <v>11.0</v>
+      </c>
+      <c r="H7" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="I7" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="J7" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="K7" s="14"/>
     </row>
     <row r="8">
       <c r="A8" s="8">
@@ -818,7 +957,7 @@
         <v>475.0</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="D8" s="10">
         <v>9100000.0</v>
@@ -827,16 +966,21 @@
         <v>1638000.0</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="G8" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="H8" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="I8" s="13"/>
-      <c r="J8" s="13"/>
+        <v>34</v>
+      </c>
+      <c r="G8" s="13">
+        <v>665.0</v>
+      </c>
+      <c r="H8" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="I8" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="J8" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="K8" s="14"/>
     </row>
     <row r="9">
       <c r="A9" s="8">
@@ -846,7 +990,7 @@
         <v>20.0</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="D9" s="10">
         <v>9900000.0</v>
@@ -855,16 +999,21 @@
         <v>1782000.0</v>
       </c>
       <c r="F9" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="G9" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="H9" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="I9" s="13"/>
-      <c r="J9" s="13"/>
+        <v>38</v>
+      </c>
+      <c r="G9" s="13">
+        <v>897.0</v>
+      </c>
+      <c r="H9" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="I9" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="J9" s="17" t="s">
+        <v>40</v>
+      </c>
+      <c r="K9" s="14"/>
     </row>
     <row r="10">
       <c r="A10" s="8">
@@ -874,7 +1023,7 @@
         <v>41.0</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="D10" s="10">
         <v>9800000.0</v>
@@ -883,16 +1032,21 @@
         <v>1764000.0</v>
       </c>
       <c r="F10" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="G10" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="H10" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="I10" s="13"/>
-      <c r="J10" s="13"/>
+        <v>42</v>
+      </c>
+      <c r="G10" s="13">
+        <v>770.0</v>
+      </c>
+      <c r="H10" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="I10" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="J10" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="K10" s="14"/>
     </row>
     <row r="11">
       <c r="A11" s="8">
@@ -902,25 +1056,30 @@
         <v>14.0</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="D11" s="10">
         <v>2.777777777E7</v>
       </c>
-      <c r="E11" s="15">
+      <c r="E11" s="16">
         <v>5000000.0</v>
       </c>
       <c r="F11" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="G11" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="H11" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="I11" s="13"/>
-      <c r="J11" s="13"/>
+        <v>46</v>
+      </c>
+      <c r="G11" s="13">
+        <v>14.0</v>
+      </c>
+      <c r="H11" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="I11" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="J11" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="K11" s="14"/>
     </row>
     <row r="12">
       <c r="A12" s="8">
@@ -930,7 +1089,7 @@
         <v>12.0</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="D12" s="10">
         <v>2.0E7</v>
@@ -939,16 +1098,21 @@
         <v>3600000.0</v>
       </c>
       <c r="F12" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="G12" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="H12" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="I12" s="13"/>
-      <c r="J12" s="13"/>
+        <v>50</v>
+      </c>
+      <c r="G12" s="13">
+        <v>12.0</v>
+      </c>
+      <c r="H12" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="I12" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="J12" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="K12" s="14"/>
     </row>
     <row r="13">
       <c r="A13" s="8">
@@ -956,7 +1120,7 @@
       </c>
       <c r="B13" s="9"/>
       <c r="C13" s="9" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="D13" s="10">
         <v>2.0E7</v>
@@ -964,15 +1128,20 @@
       <c r="E13" s="11">
         <v>3600000.0</v>
       </c>
-      <c r="F13" s="16" t="s">
-        <v>42</v>
-      </c>
-      <c r="G13" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="H13" s="13"/>
-      <c r="I13" s="13"/>
-      <c r="J13" s="13"/>
+      <c r="F13" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="G13" s="13">
+        <v>1021.0</v>
+      </c>
+      <c r="H13" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="I13" s="14"/>
+      <c r="J13" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="K13" s="14"/>
     </row>
     <row r="14">
       <c r="A14" s="8">
@@ -982,7 +1151,7 @@
         <v>480.0</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="D14" s="10">
         <v>2.0E7</v>
@@ -990,17 +1159,22 @@
       <c r="E14" s="11">
         <v>3600000.0</v>
       </c>
-      <c r="F14" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="G14" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="H14" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="I14" s="13"/>
-      <c r="J14" s="13"/>
+      <c r="F14" s="18" t="s">
+        <v>57</v>
+      </c>
+      <c r="G14" s="13">
+        <v>872.0</v>
+      </c>
+      <c r="H14" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="I14" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="J14" s="17" t="s">
+        <v>59</v>
+      </c>
+      <c r="K14" s="14"/>
     </row>
     <row r="15">
       <c r="A15" s="8">
@@ -1010,25 +1184,30 @@
         <v>33.0</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="D15" s="10">
         <v>2.777777777E7</v>
       </c>
-      <c r="E15" s="15">
+      <c r="E15" s="16">
         <v>5000000.0</v>
       </c>
-      <c r="F15" s="16" t="s">
+      <c r="F15" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="G15" s="13">
+        <v>773.0</v>
+      </c>
+      <c r="H15" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="G15" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="H15" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="I15" s="13"/>
-      <c r="J15" s="13"/>
+      <c r="I15" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="J15" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="K15" s="14"/>
     </row>
     <row r="16">
       <c r="A16" s="8">
@@ -1038,7 +1217,7 @@
         <v>19.0</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="D16" s="10">
         <v>1.03E7</v>
@@ -1046,17 +1225,22 @@
       <c r="E16" s="11">
         <v>1854000.0</v>
       </c>
-      <c r="F16" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="G16" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="H16" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="I16" s="13"/>
-      <c r="J16" s="13"/>
+      <c r="F16" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="G16" s="13">
+        <v>894.0</v>
+      </c>
+      <c r="H16" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="I16" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="J16" s="17" t="s">
+        <v>66</v>
+      </c>
+      <c r="K16" s="14"/>
     </row>
     <row r="17">
       <c r="A17" s="8">
@@ -1066,7 +1250,7 @@
         <v>21.0</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="D17" s="10">
         <v>9900000.0</v>
@@ -1074,17 +1258,22 @@
       <c r="E17" s="11">
         <v>1782000.0</v>
       </c>
-      <c r="F17" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="G17" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="H17" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="I17" s="13"/>
-      <c r="J17" s="13"/>
+      <c r="F17" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="G17" s="13">
+        <v>21.0</v>
+      </c>
+      <c r="H17" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="I17" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="J17" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="K17" s="14"/>
     </row>
     <row r="18">
       <c r="A18" s="8">
@@ -1094,25 +1283,30 @@
         <v>23.0</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>54</v>
+        <v>71</v>
       </c>
       <c r="D18" s="10">
         <v>2.0E7</v>
       </c>
-      <c r="E18" s="15">
+      <c r="E18" s="16">
         <v>4000000.0</v>
       </c>
       <c r="F18" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="G18" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="H18" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="I18" s="13"/>
-      <c r="J18" s="13"/>
+        <v>72</v>
+      </c>
+      <c r="G18" s="13">
+        <v>23.0</v>
+      </c>
+      <c r="H18" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="I18" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="J18" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="K18" s="14"/>
     </row>
     <row r="19">
       <c r="A19" s="8">
@@ -1122,7 +1316,7 @@
         <v>32.0</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="D19" s="10">
         <v>9800000.0</v>
@@ -1130,17 +1324,22 @@
       <c r="E19" s="11">
         <v>1764000.0</v>
       </c>
-      <c r="F19" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="G19" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="H19" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="I19" s="13"/>
-      <c r="J19" s="13"/>
+      <c r="F19" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="G19" s="13">
+        <v>935.0</v>
+      </c>
+      <c r="H19" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="I19" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="J19" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="K19" s="14"/>
     </row>
     <row r="20">
       <c r="A20" s="8">
@@ -1150,25 +1349,30 @@
         <v>26.0</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="D20" s="10">
         <v>2.777777777E7</v>
       </c>
-      <c r="E20" s="15">
+      <c r="E20" s="16">
         <v>5000000.0</v>
       </c>
-      <c r="F20" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="G20" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="H20" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="I20" s="13"/>
-      <c r="J20" s="13"/>
+      <c r="F20" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="G20" s="13">
+        <v>618.0</v>
+      </c>
+      <c r="H20" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="I20" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="J20" s="17" t="s">
+        <v>80</v>
+      </c>
+      <c r="K20" s="14"/>
     </row>
     <row r="21">
       <c r="A21" s="8">
@@ -1178,7 +1382,7 @@
         <v>34.0</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>63</v>
+        <v>81</v>
       </c>
       <c r="D21" s="10">
         <v>2.0E7</v>
@@ -1186,17 +1390,22 @@
       <c r="E21" s="11">
         <v>3600000.0</v>
       </c>
-      <c r="F21" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="G21" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="H21" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="I21" s="13"/>
-      <c r="J21" s="13"/>
+      <c r="F21" s="18" t="s">
+        <v>82</v>
+      </c>
+      <c r="G21" s="13">
+        <v>503.0</v>
+      </c>
+      <c r="H21" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="I21" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="J21" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="K21" s="14"/>
     </row>
     <row r="22">
       <c r="A22" s="8">
@@ -1206,7 +1415,7 @@
         <v>30.0</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>66</v>
+        <v>85</v>
       </c>
       <c r="D22" s="10">
         <v>8800000.0</v>
@@ -1214,17 +1423,22 @@
       <c r="E22" s="11">
         <v>1584000.0</v>
       </c>
-      <c r="F22" s="12" t="s">
-        <v>67</v>
-      </c>
-      <c r="G22" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="H22" s="13" t="s">
-        <v>68</v>
-      </c>
-      <c r="I22" s="13"/>
-      <c r="J22" s="13"/>
+      <c r="F22" s="18" t="s">
+        <v>86</v>
+      </c>
+      <c r="G22" s="13">
+        <v>669.0</v>
+      </c>
+      <c r="H22" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="I22" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="J22" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="K22" s="14"/>
     </row>
     <row r="23">
       <c r="A23" s="8">
@@ -1234,7 +1448,7 @@
         <v>541.0</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>69</v>
+        <v>89</v>
       </c>
       <c r="D23" s="10">
         <v>9000000.0</v>
@@ -1242,17 +1456,22 @@
       <c r="E23" s="11">
         <v>1620000.0</v>
       </c>
-      <c r="F23" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="G23" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="H23" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="I23" s="13"/>
-      <c r="J23" s="13"/>
+      <c r="F23" s="18" t="s">
+        <v>90</v>
+      </c>
+      <c r="G23" s="13">
+        <v>977.0</v>
+      </c>
+      <c r="H23" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="I23" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="J23" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="K23" s="14"/>
     </row>
     <row r="24">
       <c r="A24" s="8">
@@ -1262,25 +1481,30 @@
         <v>100.0</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>71</v>
+        <v>93</v>
       </c>
       <c r="D24" s="10">
         <v>2.777777777E7</v>
       </c>
-      <c r="E24" s="15">
+      <c r="E24" s="16">
         <v>5000000.0</v>
       </c>
-      <c r="F24" s="16" t="s">
-        <v>72</v>
-      </c>
-      <c r="G24" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="H24" s="13" t="s">
-        <v>73</v>
-      </c>
-      <c r="I24" s="13"/>
-      <c r="J24" s="13"/>
+      <c r="F24" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="G24" s="13">
+        <v>541.0</v>
+      </c>
+      <c r="H24" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="I24" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="J24" s="17" t="s">
+        <v>95</v>
+      </c>
+      <c r="K24" s="14"/>
     </row>
     <row r="25">
       <c r="A25" s="8">
@@ -1290,7 +1514,7 @@
         <v>525.0</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="D25" s="10">
         <v>8800000.0</v>
@@ -1298,17 +1522,22 @@
       <c r="E25" s="11">
         <v>1584000.0</v>
       </c>
-      <c r="F25" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="G25" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="H25" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="I25" s="13"/>
-      <c r="J25" s="13"/>
+      <c r="F25" s="18" t="s">
+        <v>97</v>
+      </c>
+      <c r="G25" s="13">
+        <v>883.0</v>
+      </c>
+      <c r="H25" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="I25" s="14" t="s">
+        <v>98</v>
+      </c>
+      <c r="J25" s="17" t="s">
+        <v>99</v>
+      </c>
+      <c r="K25" s="14"/>
     </row>
     <row r="26">
       <c r="A26" s="8">
@@ -1318,7 +1547,7 @@
         <v>524.0</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="D26" s="10">
         <v>1.0E7</v>
@@ -1326,17 +1555,22 @@
       <c r="E26" s="11">
         <v>1800000.0</v>
       </c>
-      <c r="F26" s="12" t="s">
-        <v>78</v>
-      </c>
-      <c r="G26" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="H26" s="13" t="s">
-        <v>79</v>
-      </c>
-      <c r="I26" s="13"/>
-      <c r="J26" s="13"/>
+      <c r="F26" s="18" t="s">
+        <v>101</v>
+      </c>
+      <c r="G26" s="13">
+        <v>876.0</v>
+      </c>
+      <c r="H26" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="I26" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="J26" s="17" t="s">
+        <v>103</v>
+      </c>
+      <c r="K26" s="14"/>
     </row>
     <row r="27">
       <c r="A27" s="8">
@@ -1346,7 +1580,7 @@
         <v>13.0</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>80</v>
+        <v>104</v>
       </c>
       <c r="D27" s="10">
         <v>8500000.0</v>
@@ -1354,17 +1588,22 @@
       <c r="E27" s="11">
         <v>1530000.0</v>
       </c>
-      <c r="F27" s="12" t="s">
-        <v>81</v>
-      </c>
-      <c r="G27" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="H27" s="13" t="s">
-        <v>82</v>
-      </c>
-      <c r="I27" s="13"/>
-      <c r="J27" s="13"/>
+      <c r="F27" s="18" t="s">
+        <v>105</v>
+      </c>
+      <c r="G27" s="13">
+        <v>752.0</v>
+      </c>
+      <c r="H27" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="I27" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="J27" s="17" t="s">
+        <v>107</v>
+      </c>
+      <c r="K27" s="14"/>
     </row>
     <row r="28">
       <c r="A28" s="8">
@@ -1374,7 +1613,7 @@
         <v>27.0</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>83</v>
+        <v>108</v>
       </c>
       <c r="D28" s="10">
         <v>2.0E7</v>
@@ -1382,17 +1621,22 @@
       <c r="E28" s="11">
         <v>3600000.0</v>
       </c>
-      <c r="F28" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="G28" s="13" t="s">
-        <v>85</v>
-      </c>
-      <c r="H28" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="I28" s="13"/>
-      <c r="J28" s="13"/>
+      <c r="F28" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="G28" s="13">
+        <v>513.0</v>
+      </c>
+      <c r="H28" s="14" t="s">
+        <v>110</v>
+      </c>
+      <c r="I28" s="14" t="s">
+        <v>111</v>
+      </c>
+      <c r="J28" s="17" t="s">
+        <v>112</v>
+      </c>
+      <c r="K28" s="14"/>
     </row>
     <row r="29">
       <c r="A29" s="8">
@@ -1402,7 +1646,7 @@
         <v>28.0</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="D29" s="10">
         <v>2.0E7</v>
@@ -1410,50 +1654,92 @@
       <c r="E29" s="11">
         <v>3600000.0</v>
       </c>
-      <c r="F29" s="16" t="s">
-        <v>87</v>
-      </c>
-      <c r="G29" s="13" t="s">
-        <v>85</v>
-      </c>
-      <c r="H29" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="I29" s="13"/>
-      <c r="J29" s="13"/>
+      <c r="F29" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="G29" s="19">
+        <v>534.0</v>
+      </c>
+      <c r="H29" s="14" t="s">
+        <v>110</v>
+      </c>
+      <c r="I29" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="J29" s="17" t="s">
+        <v>115</v>
+      </c>
+      <c r="K29" s="14"/>
     </row>
     <row r="30">
-      <c r="A30" s="17">
+      <c r="A30" s="20">
         <v>46261.0</v>
       </c>
       <c r="B30" s="9"/>
-      <c r="C30" s="16" t="s">
-        <v>89</v>
+      <c r="C30" s="12" t="s">
+        <v>116</v>
       </c>
       <c r="D30" s="10">
         <v>2.777777777E7</v>
       </c>
-      <c r="E30" s="15">
+      <c r="E30" s="16">
         <v>5000000.0</v>
       </c>
-      <c r="F30" s="16" t="s">
-        <v>90</v>
-      </c>
-      <c r="G30" s="13" t="s">
-        <v>85</v>
-      </c>
-      <c r="H30" s="13"/>
-      <c r="I30" s="13"/>
-      <c r="J30" s="13"/>
+      <c r="F30" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="G30" s="14">
+        <v>933.0</v>
+      </c>
+      <c r="H30" s="14" t="s">
+        <v>110</v>
+      </c>
+      <c r="I30" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="J30" s="17" t="s">
+        <v>119</v>
+      </c>
+      <c r="K30" s="14"/>
     </row>
   </sheetData>
-  <autoFilter ref="$A$1:$G$30">
-    <sortState ref="A1:G30">
+  <autoFilter ref="$A$1:$H$30">
+    <sortState ref="A1:H30">
       <sortCondition ref="A1:A30"/>
       <sortCondition descending="1" ref="E1:E30"/>
       <sortCondition descending="1" ref="D1:D30"/>
     </sortState>
   </autoFilter>
-  <drawing r:id="rId1"/>
+  <hyperlinks>
+    <hyperlink r:id="rId1" ref="J3"/>
+    <hyperlink r:id="rId2" ref="J4"/>
+    <hyperlink r:id="rId3" ref="J5"/>
+    <hyperlink r:id="rId4" ref="J6"/>
+    <hyperlink r:id="rId5" ref="J7"/>
+    <hyperlink r:id="rId6" ref="J8"/>
+    <hyperlink r:id="rId7" ref="J9"/>
+    <hyperlink r:id="rId8" ref="J10"/>
+    <hyperlink r:id="rId9" ref="J11"/>
+    <hyperlink r:id="rId10" ref="J12"/>
+    <hyperlink r:id="rId11" ref="J13"/>
+    <hyperlink r:id="rId12" ref="J14"/>
+    <hyperlink r:id="rId13" ref="J15"/>
+    <hyperlink r:id="rId14" ref="J16"/>
+    <hyperlink r:id="rId15" ref="J17"/>
+    <hyperlink r:id="rId16" ref="J18"/>
+    <hyperlink r:id="rId17" ref="J19"/>
+    <hyperlink r:id="rId18" ref="J20"/>
+    <hyperlink r:id="rId19" ref="J21"/>
+    <hyperlink r:id="rId20" ref="J22"/>
+    <hyperlink r:id="rId21" ref="J23"/>
+    <hyperlink r:id="rId22" ref="J24"/>
+    <hyperlink r:id="rId23" ref="J25"/>
+    <hyperlink r:id="rId24" ref="J26"/>
+    <hyperlink r:id="rId25" ref="J27"/>
+    <hyperlink r:id="rId26" ref="J28"/>
+    <hyperlink r:id="rId27" ref="J29"/>
+    <hyperlink r:id="rId28" ref="J30"/>
+  </hyperlinks>
+  <drawing r:id="rId29"/>
 </worksheet>
 </file>
--- a/Data/MST/OAD_2026_Schedule.xlsx
+++ b/Data/MST/OAD_2026_Schedule.xlsx
@@ -869,8 +869,8 @@
       <c r="F5" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="G5" s="13">
-        <v>734.0</v>
+      <c r="G5" s="14">
+        <v>928.0</v>
       </c>
       <c r="H5" s="14" t="s">
         <v>12</v>
